--- a/data/gas_flows.xlsx
+++ b/data/gas_flows.xlsx
@@ -1228,7 +1228,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>iuk</t>
+          <t>interconnector</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">

--- a/data/gas_flows.xlsx
+++ b/data/gas_flows.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,40 +451,45 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>avonmouth</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>hatfield_moor</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>hill_top_farm</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>holehouse_farm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>holford</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>hornsea</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>humbly_grove</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>rough</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>stublach</t>
         </is>
@@ -500,27 +505,30 @@
         <v>6</v>
       </c>
       <c r="C2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D2" t="n">
         <v>1.5</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>0.8</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>0.7</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>4.5</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>5.2</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>2.1</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>5.5</v>
       </c>
     </row>
@@ -534,27 +542,30 @@
         <v>6.2</v>
       </c>
       <c r="C3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D3" t="n">
         <v>1.6</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>0.8</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>0.7</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>4.7</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>5.3</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>2.1</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>9</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>5.6</v>
       </c>
     </row>
@@ -568,27 +579,30 @@
         <v>5.8</v>
       </c>
       <c r="C4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D4" t="n">
         <v>1.5</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.7</v>
       </c>
       <c r="E4" t="n">
         <v>0.7</v>
       </c>
       <c r="F4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G4" t="n">
         <v>4.3</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>5.1</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>2</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>5.6</v>
       </c>
     </row>
@@ -602,27 +616,30 @@
         <v>5.6</v>
       </c>
       <c r="C5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D5" t="n">
         <v>1.4</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>0.7</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>0.6</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>4.2</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>5</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>1.9</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>8.5</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>5.6</v>
       </c>
     </row>
@@ -636,27 +653,30 @@
         <v>6.1</v>
       </c>
       <c r="C6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D6" t="n">
         <v>1.6</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>0.8</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>0.7</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>4.6</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>5.2</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>2.1</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>9</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>5.6</v>
       </c>
     </row>
@@ -670,27 +690,30 @@
         <v>6.3</v>
       </c>
       <c r="C7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D7" t="n">
         <v>1.6</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.8</v>
       </c>
       <c r="E7" t="n">
         <v>0.8</v>
       </c>
       <c r="F7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G7" t="n">
         <v>4.7</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>5.4</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>2.2</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>9</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>5.4</v>
       </c>
     </row>
@@ -704,27 +727,30 @@
         <v>6.2</v>
       </c>
       <c r="C8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D8" t="n">
         <v>1.6</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>0.8</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>0.7</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>4.6</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>5.3</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>2.1</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>9</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>5.6</v>
       </c>
     </row>

--- a/data/gas_flows.xlsx
+++ b/data/gas_flows.xlsx
@@ -319,13 +319,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-172</v>
+        <v>-203.65788</v>
       </c>
       <c r="C2" t="n">
-        <v>-48</v>
+        <v>-16.20376</v>
       </c>
       <c r="D2" t="n">
-        <v>-24</v>
+        <v>-2.29531</v>
       </c>
     </row>
     <row r="3">
@@ -335,13 +335,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-174</v>
+        <v>-229.48924</v>
       </c>
       <c r="C3" t="n">
-        <v>-49</v>
+        <v>-21.46895</v>
       </c>
       <c r="D3" t="n">
-        <v>-24.5</v>
+        <v>-2.39829</v>
       </c>
     </row>
     <row r="4">
@@ -351,13 +351,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-169</v>
+        <v>-241.29634</v>
       </c>
       <c r="C4" t="n">
-        <v>-50</v>
+        <v>-21.66661</v>
       </c>
       <c r="D4" t="n">
-        <v>-25</v>
+        <v>-2.38093</v>
       </c>
     </row>
     <row r="5">
@@ -367,13 +367,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-171.5</v>
+        <v>-251.11051</v>
       </c>
       <c r="C5" t="n">
-        <v>-47</v>
+        <v>-58.36815</v>
       </c>
       <c r="D5" t="n">
-        <v>-24</v>
+        <v>-2.88077</v>
       </c>
     </row>
     <row r="6">
@@ -383,13 +383,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-176</v>
+        <v>-275.92175</v>
       </c>
       <c r="C6" t="n">
-        <v>-46.5</v>
+        <v>-97.95877</v>
       </c>
       <c r="D6" t="n">
-        <v>-23.5</v>
+        <v>-6.19222</v>
       </c>
     </row>
     <row r="7">
@@ -399,13 +399,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-180</v>
+        <v>-271.45103</v>
       </c>
       <c r="C7" t="n">
-        <v>-45</v>
+        <v>-77.06984</v>
       </c>
       <c r="D7" t="n">
-        <v>-23</v>
+        <v>-5.02446</v>
       </c>
     </row>
     <row r="8">
@@ -415,13 +415,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-177.5</v>
+        <v>-234.58712</v>
       </c>
       <c r="C8" t="n">
-        <v>-46</v>
+        <v>-75.24306</v>
       </c>
       <c r="D8" t="n">
-        <v>-24.2</v>
+        <v>-3.83571</v>
       </c>
     </row>
   </sheetData>
@@ -797,13 +797,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>17.694</v>
       </c>
       <c r="C2" t="n">
-        <v>19</v>
+        <v>4.117</v>
       </c>
       <c r="D2" t="n">
-        <v>22</v>
+        <v>39.683</v>
       </c>
     </row>
     <row r="3">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16.5</v>
+        <v>18.934</v>
       </c>
       <c r="C3" t="n">
-        <v>19.2</v>
+        <v>15.135</v>
       </c>
       <c r="D3" t="n">
-        <v>22.5</v>
+        <v>39.525</v>
       </c>
     </row>
     <row r="4">
@@ -829,13 +829,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15.5</v>
+        <v>18.925</v>
       </c>
       <c r="C4" t="n">
-        <v>18.6</v>
+        <v>19.618</v>
       </c>
       <c r="D4" t="n">
-        <v>21.5</v>
+        <v>49.925</v>
       </c>
     </row>
     <row r="5">
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15.8</v>
+        <v>18.778</v>
       </c>
       <c r="C5" t="n">
-        <v>18.9</v>
+        <v>26.595</v>
       </c>
       <c r="D5" t="n">
-        <v>21.7</v>
+        <v>49.938</v>
       </c>
     </row>
     <row r="6">
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16.2</v>
+        <v>24.451</v>
       </c>
       <c r="C6" t="n">
-        <v>19.3</v>
+        <v>42.273</v>
       </c>
       <c r="D6" t="n">
-        <v>22.5</v>
+        <v>60.076</v>
       </c>
     </row>
     <row r="7">
@@ -877,13 +877,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16.8</v>
+        <v>23.966</v>
       </c>
       <c r="C7" t="n">
-        <v>19.5</v>
+        <v>41.013</v>
       </c>
       <c r="D7" t="n">
-        <v>22.8</v>
+        <v>59.108</v>
       </c>
     </row>
     <row r="8">
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16.1</v>
+        <v>19.388</v>
       </c>
       <c r="C8" t="n">
-        <v>19.1</v>
+        <v>46.704</v>
       </c>
       <c r="D8" t="n">
-        <v>22.3</v>
+        <v>60.081</v>
       </c>
     </row>
   </sheetData>
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>6.5</v>
+        <v>15.884</v>
       </c>
     </row>
     <row r="3">
@@ -1291,13 +1291,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>6.7</v>
+        <v>19.041</v>
       </c>
     </row>
     <row r="4">
@@ -1307,13 +1307,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15.8</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>12.3</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>6.9</v>
+        <v>21.157</v>
       </c>
     </row>
     <row r="5">
@@ -1323,13 +1323,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15.6</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>12.2</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>24.57</v>
       </c>
     </row>
     <row r="6">
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14.9</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>6.4</v>
+        <v>26.746</v>
       </c>
     </row>
     <row r="7">
@@ -1355,13 +1355,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14.8</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>6.4</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="8">
@@ -1371,13 +1371,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>0.63095</v>
       </c>
       <c r="C8" t="n">
-        <v>12.6</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>6.9</v>
+        <v>24.248</v>
       </c>
     </row>
   </sheetData>

--- a/data/gas_flows.xlsx
+++ b/data/gas_flows.xlsx
@@ -502,34 +502,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.4</v>
+        <v>7.57782</v>
       </c>
       <c r="D2" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8</v>
+        <v>3.29309</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>4.5</v>
+        <v>13.25299</v>
       </c>
       <c r="H2" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>5.5</v>
+        <v>9.581530000000001</v>
       </c>
     </row>
     <row r="3">
@@ -539,34 +536,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.4</v>
+        <v>4.43378</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>4.7</v>
+        <v>10.89684</v>
       </c>
       <c r="H3" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -576,34 +570,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7</v>
+        <v>0.47058</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>4.3</v>
+        <v>3.29011</v>
       </c>
       <c r="H4" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -613,34 +604,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -650,34 +638,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -687,34 +672,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -724,34 +706,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8</v>
+        <v>0.5851499999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/gas_flows.xlsx
+++ b/data/gas_flows.xlsx
@@ -959,34 +959,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>18</v>
+        <v>43.421</v>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>20.274</v>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
-      </c>
-      <c r="F2" t="n">
-        <v>3.5</v>
+        <v>25.114</v>
       </c>
       <c r="G2" t="n">
-        <v>10</v>
+        <v>8.634</v>
       </c>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>4.634</v>
       </c>
       <c r="I2" t="n">
-        <v>11</v>
+        <v>7.937</v>
       </c>
       <c r="J2" t="n">
-        <v>8</v>
+        <v>4.4</v>
       </c>
       <c r="K2" t="n">
-        <v>14.5</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="3">
@@ -996,34 +993,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24.2</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>18.1</v>
+        <v>43.696</v>
       </c>
       <c r="D3" t="n">
-        <v>16.2</v>
+        <v>18.185</v>
       </c>
       <c r="E3" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="F3" t="n">
-        <v>3.6</v>
+        <v>25.096</v>
       </c>
       <c r="G3" t="n">
-        <v>10.1</v>
+        <v>8.734</v>
       </c>
       <c r="H3" t="n">
-        <v>6.1</v>
+        <v>4.615</v>
       </c>
       <c r="I3" t="n">
-        <v>11.1</v>
+        <v>8.297000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>8.1</v>
+        <v>4.4</v>
       </c>
       <c r="K3" t="n">
-        <v>14.4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="4">
@@ -1033,34 +1027,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24.1</v>
+        <v>74.08</v>
       </c>
       <c r="C4" t="n">
-        <v>18</v>
+        <v>39.237</v>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>18.177</v>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
-      </c>
-      <c r="F4" t="n">
-        <v>3.5</v>
+        <v>24.577</v>
       </c>
       <c r="G4" t="n">
-        <v>10</v>
+        <v>7.486</v>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>4.444</v>
       </c>
       <c r="I4" t="n">
-        <v>11</v>
+        <v>7.285</v>
       </c>
       <c r="J4" t="n">
-        <v>8</v>
+        <v>4.39</v>
       </c>
       <c r="K4" t="n">
-        <v>14.5</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="5">
@@ -1070,34 +1061,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.8</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>17.8</v>
+        <v>41.83</v>
       </c>
       <c r="D5" t="n">
-        <v>15.9</v>
+        <v>19.58</v>
       </c>
       <c r="E5" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="F5" t="n">
-        <v>3.4</v>
+        <v>23.894</v>
       </c>
       <c r="G5" t="n">
-        <v>9.9</v>
+        <v>6.852</v>
       </c>
       <c r="H5" t="n">
-        <v>5.9</v>
+        <v>4.497</v>
       </c>
       <c r="I5" t="n">
-        <v>10.9</v>
+        <v>5.406</v>
       </c>
       <c r="J5" t="n">
-        <v>7.9</v>
+        <v>4.39</v>
       </c>
       <c r="K5" t="n">
-        <v>14.8</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="6">
@@ -1107,34 +1095,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24</v>
+        <v>74.06</v>
       </c>
       <c r="C6" t="n">
-        <v>18.1</v>
+        <v>35.872</v>
       </c>
       <c r="D6" t="n">
-        <v>16.1</v>
+        <v>19.911</v>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
-      </c>
-      <c r="F6" t="n">
-        <v>3.5</v>
+        <v>23.596</v>
       </c>
       <c r="G6" t="n">
-        <v>10</v>
+        <v>7.024</v>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>4.205</v>
       </c>
       <c r="I6" t="n">
-        <v>11.1</v>
+        <v>5.258</v>
       </c>
       <c r="J6" t="n">
-        <v>8.1</v>
+        <v>4.35</v>
       </c>
       <c r="K6" t="n">
-        <v>14.7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -1144,34 +1129,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24.3</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>18.2</v>
+        <v>38.639</v>
       </c>
       <c r="D7" t="n">
-        <v>16.1</v>
+        <v>19.94</v>
       </c>
       <c r="E7" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="F7" t="n">
-        <v>3.6</v>
+        <v>24.675</v>
       </c>
       <c r="G7" t="n">
-        <v>10.1</v>
+        <v>7.819</v>
       </c>
       <c r="H7" t="n">
-        <v>6.1</v>
+        <v>4.031</v>
       </c>
       <c r="I7" t="n">
-        <v>11.2</v>
+        <v>5.445</v>
       </c>
       <c r="J7" t="n">
-        <v>8.1</v>
+        <v>4.25</v>
       </c>
       <c r="K7" t="n">
-        <v>14.6</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="8">
@@ -1181,34 +1163,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>18.1</v>
+        <v>27.482</v>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>20.392</v>
       </c>
       <c r="E8" t="n">
-        <v>7</v>
-      </c>
-      <c r="F8" t="n">
-        <v>3.5</v>
+        <v>25.054</v>
       </c>
       <c r="G8" t="n">
-        <v>10</v>
+        <v>7.419</v>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>3.616</v>
       </c>
       <c r="I8" t="n">
-        <v>11.1</v>
+        <v>5.831</v>
       </c>
       <c r="J8" t="n">
-        <v>8.1</v>
+        <v>4.06</v>
       </c>
       <c r="K8" t="n">
-        <v>15.2</v>
+        <v>4.09</v>
       </c>
     </row>
   </sheetData>
